--- a/AtchisonRegime/Outputs/Canada/df_regSummary_Canada.xlsx
+++ b/AtchisonRegime/Outputs/Canada/df_regSummary_Canada.xlsx
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G2" t="n">
-        <v>1.029800213558017</v>
+        <v>1.037985084197179</v>
       </c>
       <c r="H2" t="n">
-        <v>3.285481825592969</v>
+        <v>3.269506640637442</v>
       </c>
       <c r="I2" t="n">
         <v>-5.44746782875864</v>
@@ -545,16 +545,16 @@
         <v>11.6865661939146</v>
       </c>
       <c r="K2" t="n">
-        <v>30.79365079365079</v>
+        <v>31.0126582278481</v>
       </c>
       <c r="L2" t="n">
         <v>11</v>
       </c>
       <c r="M2" t="n">
-        <v>8.818181818181818</v>
+        <v>8.909090909090908</v>
       </c>
       <c r="N2" t="n">
-        <v>0.100491971764367</v>
+        <v>0.1025922794268394</v>
       </c>
       <c r="O2" t="n">
         <v>-0.1294058302292806</v>
@@ -603,7 +603,7 @@
         <v>9.151803599435841</v>
       </c>
       <c r="K3" t="n">
-        <v>17.14285714285714</v>
+        <v>17.08860759493671</v>
       </c>
       <c r="L3" t="n">
         <v>12</v>
@@ -661,7 +661,7 @@
         <v>8.087478763970051</v>
       </c>
       <c r="K4" t="n">
-        <v>18.41269841269841</v>
+        <v>18.35443037974684</v>
       </c>
       <c r="L4" t="n">
         <v>10</v>
@@ -719,7 +719,7 @@
         <v>9.70751728527032</v>
       </c>
       <c r="K5" t="n">
-        <v>33.65079365079365</v>
+        <v>33.54430379746836</v>
       </c>
       <c r="L5" t="n">
         <v>12</v>
